--- a/content/02_리서치/2026-06-30_API비용산정_근거.xlsx
+++ b/content/02_리서치/2026-06-30_API비용산정_근거.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,6 +89,11 @@
     </font>
     <font>
       <name val="Malgun Gothic"/>
+      <color rgb="00999999"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
       <color rgb="00444444"/>
       <sz val="9"/>
     </font>
@@ -164,6 +169,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C05C00"/>
       </patternFill>
     </fill>
@@ -185,11 +195,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEBEE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -211,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -237,6 +242,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -263,7 +271,9 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -277,32 +287,41 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="14" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="15" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -673,15 +692,15 @@
   <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -766,7 +785,7 @@
         </is>
       </c>
       <c r="D7" s="10">
-        <f>B7*1</f>
+        <f>B7</f>
         <v/>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -789,7 +808,7 @@
           <t>1개월</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -813,7 +832,7 @@
         </is>
       </c>
       <c r="D9" s="10">
-        <f>B9*1</f>
+        <f>B9</f>
         <v/>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -823,108 +842,107 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>AWS (EC2·S3·RDS 통합 예비 예산)</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>1개월</t>
         </is>
       </c>
-      <c r="D10" s="13">
-        <f>B10*1</f>
-        <v/>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="D10" s="14">
+        <f>B10</f>
+        <v/>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Free Tier 만료 대비 고정 예비 예산</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>▼ Claude Code — Option 선택 (A / B 중 하나 선택)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>[Option A] Claude Code Pro × 6명</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>6명 × 1개월</t>
         </is>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="18">
         <f>B12*6</f>
         <v/>
       </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>Pro $20/유저 — 기본 사용량</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>Pro $20/유저</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>[Option B] Claude Code Max × 4 + Pro × 2</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>Max $100 × 4
-+ Pro $20 × 2</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>Max×4 + Pro×2</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>6명 × 1개월</t>
         </is>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="22" t="n">
         <v>440</v>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>Max $100 (BE2·FE1·UX1) + Pro $20 (PM2) — 업그레이드 불가 시 권장</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>소계 ① — Option A 기준</t>
         </is>
       </c>
-      <c r="B14" s="23" t="n"/>
-      <c r="C14" s="23" t="n"/>
-      <c r="D14" s="24">
+      <c r="B14" s="24" t="n"/>
+      <c r="C14" s="24" t="n"/>
+      <c r="D14" s="25">
         <f>D7+D8+D9+D10+D12</f>
         <v/>
       </c>
-      <c r="E14" s="25" t="inlineStr">
-        <is>
-          <t>※ Option B 기준: =D7+D8+D9+D10+D13 → $510</t>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>※ Option B 기준 소계: $510</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
-        <is>
-          <t>② 이미지 생성 API  (GPT Image 2 단일 모델)</t>
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>② 이미지 생성 API  (GPT Image 2 단일 모델, quality: medium)</t>
         </is>
       </c>
     </row>
@@ -982,50 +1000,50 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>GPT Image 2 medium — 9그리드 스토리보드</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="D19" s="10">
-        <f>B19*C19</f>
-        <v/>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>F003-B 스토리보드 이미지 (1세트 = 이미지 1장)</t>
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>[B팀 제공] 9그리드 스토리보드 이미지</t>
+        </is>
+      </c>
+      <c r="B19" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="29" t="inlineStr">
+        <is>
+          <t>B팀에서 생성·제공 → A2팀 비용 없음</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>소계 ②</t>
         </is>
       </c>
-      <c r="B20" s="23" t="n"/>
-      <c r="D20" s="24">
-        <f>SUM(D18:D19)</f>
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="24" t="n"/>
+      <c r="D20" s="25">
+        <f>D18</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t>③ 영상 생성 API  (1세트 = 1클립)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ℹ️  흐름: [B] 9그리드 스토리보드 이미지 1장 + shot1~9 전체 프롬프트 생성  →  [A] 영상 생성 API 입력  →  클립 1개 출력</t>
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ℹ️  흐름: [B팀] 9그리드 스토리보드 + shot1~9 프롬프트 제공  →  [A2팀] 영상 생성 API 입력  →  클립 1개 출력</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1101,7 @@
       <c r="D25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="33">
         <f>C25*D25</f>
         <v/>
       </c>
@@ -1093,18 +1111,18 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>개발 테스트 8회 (주 2회 × 4주)</t>
+          <t>주 2회 × 4주, 3~5초 상한 기준</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>fal.ai Seedance — 중간점검 (5초/클립)</t>
+          <t>fal.ai Seedance 2.0 — 중간점검 (5초/클립)</t>
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>0.3</v>
+        <v>0.3034</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>1</v>
@@ -1112,7 +1130,7 @@
       <c r="D26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="33">
         <f>C26*D26</f>
         <v/>
       </c>
@@ -1122,26 +1140,26 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>2주차 중간점검 데모</t>
+          <t>2주차 중간점검 데모 / 720p standard</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>fal.ai Seedance — 최종 데모 (10초/클립)</t>
+          <t>fal.ai Seedance 2.0 — 최종 출력 (15초/클립, 최대 길이)</t>
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>0.3</v>
+        <v>0.3034</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" s="29">
+        <v>15</v>
+      </c>
+      <c r="E27" s="33">
         <f>C27*D27</f>
         <v/>
       </c>
@@ -1151,31 +1169,31 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>4주차 최종 발표 (2세트)</t>
+          <t>4주차 최종 발표 (2세트) / 720p standard / 음성 포함</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>소계 ③</t>
         </is>
       </c>
-      <c r="B28" s="23" t="n"/>
-      <c r="F28" s="24">
+      <c r="B28" s="24" t="n"/>
+      <c r="F28" s="25">
         <f>SUM(F25:F27)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ★ fal.ai Hard Limit 권장: $50 설정 (Billing &gt; Spend Limit — 비용 폭탄 방지)</t>
+      <c r="A29" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ★ fal.ai Hard Limit 권장: $50 설정 (Billing &gt; Spend Limit)  |  Seedance 2.0 참고: fal.ai/models/bytedance/seedance-2.0/text-to-video</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="31" t="inlineStr">
+      <c r="A31" s="35" t="inlineStr">
         <is>
           <t>④ Claude Sonnet API  (토큰 기반)</t>
         </is>
@@ -1227,7 +1245,7 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Claude Sonnet — 프롬프트 보조 (F001·F003-B)</t>
+          <t>Claude Sonnet — 프롬프트 보조 (F001 이미지 생성)</t>
         </is>
       </c>
       <c r="B33" s="9" t="n">
@@ -1251,14 +1269,14 @@
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>이미지·스토리보드 프롬프트 생성 보조</t>
+          <t>이미지 프롬프트 생성 보조</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Claude Sonnet — 역프롬프트 (F004, S등급)</t>
+          <t>Claude Sonnet — 역프롬프트 (F004, S등급 도전)</t>
         </is>
       </c>
       <c r="B34" s="9" t="n">
@@ -1287,19 +1305,19 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="A35" s="23" t="inlineStr">
         <is>
           <t>소계 ④</t>
         </is>
       </c>
-      <c r="B35" s="23" t="n"/>
-      <c r="G35" s="24">
+      <c r="B35" s="24" t="n"/>
+      <c r="G35" s="25">
         <f>SUM(G33:G34)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="32" t="inlineStr">
+      <c r="A37" s="36" t="inlineStr">
         <is>
           <t>⑤ 등급별 예산 요약  (×1.5 여유 포함)</t>
         </is>
@@ -1318,7 +1336,7 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>순 비용 ($)</t>
+          <t>API 순비용 ($)</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -1333,12 +1351,12 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Option A 툴비용</t>
+          <t>Option A 합산 ($)</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>Option B 툴비용</t>
+          <t>Option B 합산 ($)</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
@@ -1351,24 +1369,23 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>공통 필수
-(B등급 달성)</t>
+          <t>B등급</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>② 이미지 + ③ 영상(테스트) + ④ 프롬프트 보조</t>
+          <t>② 이미지 + ③ 영상(Kling 테스트+Seedance 중간) + ④ 프롬프트 보조</t>
         </is>
       </c>
       <c r="C39" s="10">
-        <f>D20+F28+G35</f>
+        <f>D20+F25+F26+G33</f>
         <v/>
       </c>
       <c r="D39" s="10">
         <f>C39*1.5</f>
         <v/>
       </c>
-      <c r="E39" s="29">
+      <c r="E39" s="33">
         <f>D39*C3</f>
         <v/>
       </c>
@@ -1394,18 +1411,18 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>B등급 전체 + ④ 역프롬프트 (F004)</t>
+          <t>B등급 전체 + Seedance 2.0 최종 15초 + ④ 역프롬프트 (F004)</t>
         </is>
       </c>
       <c r="C40" s="10">
-        <f>C39+G34</f>
+        <f>D20+F27+G34+G34</f>
         <v/>
       </c>
       <c r="D40" s="10">
         <f>C40*1.5</f>
         <v/>
       </c>
-      <c r="E40" s="29">
+      <c r="E40" s="33">
         <f>D40*C3</f>
         <v/>
       </c>
@@ -1419,75 +1436,75 @@
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>역프롬프트 재생성 루프 포함</t>
+          <t>역프롬프트 재생성 루프 포함 / Seedance 2.0 최대 길이 기준</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="33" t="inlineStr">
+      <c r="A41" s="37" t="inlineStr">
         <is>
           <t>★ 최종 신청 권장 (S등급 기준)</t>
         </is>
       </c>
-      <c r="B41" s="23" t="n"/>
-      <c r="C41" s="34">
+      <c r="B41" s="24" t="n"/>
+      <c r="C41" s="38">
         <f>C40</f>
         <v/>
       </c>
-      <c r="D41" s="34">
+      <c r="D41" s="38">
         <f>D40</f>
         <v/>
       </c>
-      <c r="E41" s="35">
+      <c r="E41" s="39">
         <f>E40</f>
         <v/>
       </c>
-      <c r="F41" s="34">
+      <c r="F41" s="38">
         <f>F40</f>
         <v/>
       </c>
-      <c r="G41" s="34">
+      <c r="G41" s="38">
         <f>G40</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="26" t="inlineStr">
+      <c r="A43" s="27" t="inlineStr">
         <is>
           <t>⑥ 비용 절감 수칙 (참고)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="36" t="inlineStr">
+      <c r="A44" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  ① GPT Image 2 quality: medium 고정 — high 대비 약 75% 절감</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ② Claude 프롬프트는 간결하게 유지 — 불필요한 토큰 절감</t>
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ② 개발 테스트는 Kling (저가) 우선, 중간점검·최종만 Seedance 2.0 사용</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ③ fal.ai Hard Limit $50 설정 필수 — 대시보드 &gt; Billing &gt; Spend Limit</t>
+      <c r="A46" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ③ Claude 프롬프트는 간결하게 유지 — 불필요한 토큰 절감</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ④ 영상 클립 5~10초 이내 유지 — 초당 과금이므로 길수록 비용 급증</t>
+      <c r="A47" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ④ fal.ai Hard Limit $50 설정 필수 — 대시보드 &gt; Billing &gt; Spend Limit</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="36" t="inlineStr">
+      <c r="A48" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  ⑤ 주 1회 각 API 대시보드 사용량 확인 (OpenAI / fal.ai / Anthropic Console / AWS)</t>
         </is>
@@ -1505,13 +1522,13 @@
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="A43:I43"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="A31:I31"/>
     <mergeCell ref="A48:I48"/>
     <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A11:I11"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A1:I1"/>

--- a/content/02_리서치/2026-06-30_API비용산정_근거.xlsx
+++ b/content/02_리서치/2026-06-30_API비용산정_근거.xlsx
@@ -216,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -224,9 +224,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -241,7 +245,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -251,7 +254,9 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -261,11 +266,13 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -293,7 +300,7 @@
     <xf numFmtId="0" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -302,7 +309,9 @@
     <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -694,13 +703,13 @@
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -808,7 +817,7 @@
           <t>1개월</t>
         </is>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -842,105 +851,105 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>AWS (EC2·S3·RDS 통합 예비 예산)</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>1개월</t>
         </is>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="13">
         <f>B10</f>
         <v/>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Free Tier 만료 대비 고정 예비 예산</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>▼ Claude Code — Option 선택 (A / B 중 하나 선택)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>[Option A] Claude Code Pro × 6명</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>6명 × 1개월</t>
         </is>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="17">
         <f>B12*6</f>
         <v/>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>Pro $20/유저</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>[Option B] Claude Code Max × 4 + Pro × 2</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>Max×4 + Pro×2</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>6명 × 1개월</t>
         </is>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="21" t="n">
         <v>440</v>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>Max $100 (BE2·FE1·UX1) + Pro $20 (PM2) — 업그레이드 불가 시 권장</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>소계 ① — Option A 기준</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="n"/>
-      <c r="C14" s="24" t="n"/>
-      <c r="D14" s="25">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>소계 ① — Option A 기준  ($195)</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="n"/>
+      <c r="C14" s="23" t="n"/>
+      <c r="D14" s="24">
         <f>D7+D8+D9+D10+D12</f>
         <v/>
       </c>
-      <c r="E14" s="26" t="inlineStr">
-        <is>
-          <t>※ Option B 기준 소계: $510</t>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>※ Option B 기준: $515</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>② 이미지 생성 API  (GPT Image 2 단일 모델, quality: medium)</t>
         </is>
@@ -1000,48 +1009,48 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="28" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>[B팀 제공] 9그리드 스토리보드 이미지</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="30" t="n">
+      <c r="D19" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="29" t="inlineStr">
+      <c r="E19" s="28" t="inlineStr">
         <is>
           <t>B팀에서 생성·제공 → A2팀 비용 없음</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
-        <is>
-          <t>소계 ②</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="n"/>
-      <c r="C20" s="24" t="n"/>
-      <c r="D20" s="25">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>소계 ②  ($5.04)</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="24">
         <f>D18</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>③ 영상 생성 API  (1세트 = 1클립)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  ℹ️  흐름: [B팀] 9그리드 스토리보드 + shot1~9 프롬프트 제공  →  [A2팀] 영상 생성 API 입력  →  클립 1개 출력</t>
         </is>
@@ -1101,7 +1110,7 @@
       <c r="D25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="32">
         <f>C25*D25</f>
         <v/>
       </c>
@@ -1111,7 +1120,7 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>주 2회 × 4주, 3~5초 상한 기준</t>
+          <t>주 2회 × 4주 / 3~5초 상한 기준</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1139,7 @@
       <c r="D26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E26" s="33">
+      <c r="E26" s="32">
         <f>C26*D26</f>
         <v/>
       </c>
@@ -1159,7 +1168,7 @@
       <c r="D27" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="32">
         <f>C27*D27</f>
         <v/>
       </c>
@@ -1174,26 +1183,26 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="inlineStr">
-        <is>
-          <t>소계 ③</t>
-        </is>
-      </c>
-      <c r="B28" s="24" t="n"/>
-      <c r="F28" s="25">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>소계 ③  ($15.02)</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="n"/>
+      <c r="F28" s="24">
         <f>SUM(F25:F27)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ★ fal.ai Hard Limit 권장: $50 설정 (Billing &gt; Spend Limit)  |  Seedance 2.0 참고: fal.ai/models/bytedance/seedance-2.0/text-to-video</t>
+      <c r="A29" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ★ fal.ai Hard Limit 권장: $50 설정 (Billing &gt; Spend Limit)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="35" t="inlineStr">
+      <c r="A31" s="34" t="inlineStr">
         <is>
           <t>④ Claude Sonnet API  (토큰 기반)</t>
         </is>
@@ -1305,19 +1314,19 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>소계 ④</t>
-        </is>
-      </c>
-      <c r="B35" s="24" t="n"/>
-      <c r="G35" s="25">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>소계 ④  ($8.18)</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="n"/>
+      <c r="G35" s="24">
         <f>SUM(G33:G34)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="36" t="inlineStr">
+      <c r="A37" s="35" t="inlineStr">
         <is>
           <t>⑤ 등급별 예산 요약  (×1.5 여유 포함)</t>
         </is>
@@ -1366,7 +1375,7 @@
       </c>
       <c r="I38" s="7" t="inlineStr"/>
     </row>
-    <row r="39" ht="30" customHeight="1">
+    <row r="39" ht="28" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
           <t>B등급</t>
@@ -1374,7 +1383,7 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>② 이미지 + ③ 영상(Kling 테스트+Seedance 중간) + ④ 프롬프트 보조</t>
+          <t>② 이미지 + ③ Kling·Seedance중간 + ④ 프롬프트 보조</t>
         </is>
       </c>
       <c r="C39" s="10">
@@ -1385,7 +1394,7 @@
         <f>C39*1.5</f>
         <v/>
       </c>
-      <c r="E39" s="33">
+      <c r="E39" s="32">
         <f>D39*C3</f>
         <v/>
       </c>
@@ -1394,7 +1403,7 @@
         <v/>
       </c>
       <c r="G39" s="10">
-        <f>D39+510</f>
+        <f>D39+515</f>
         <v/>
       </c>
       <c r="H39" s="9" t="inlineStr">
@@ -1403,7 +1412,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1">
+    <row r="40" ht="28" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
           <t>S등급 (도전)</t>
@@ -1411,18 +1420,18 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>B등급 전체 + Seedance 2.0 최종 15초 + ④ 역프롬프트 (F004)</t>
+          <t>B등급 전체 + ③ Seedance 최종 15초 + ④ 역프롬프트 (F004)</t>
         </is>
       </c>
       <c r="C40" s="10">
-        <f>D20+F27+G34+G34</f>
+        <f>D20+F25+F26+F27+G33+G34</f>
         <v/>
       </c>
       <c r="D40" s="10">
         <f>C40*1.5</f>
         <v/>
       </c>
-      <c r="E40" s="33">
+      <c r="E40" s="32">
         <f>D40*C3</f>
         <v/>
       </c>
@@ -1431,7 +1440,7 @@
         <v/>
       </c>
       <c r="G40" s="10">
-        <f>D40+510</f>
+        <f>D40+515</f>
         <v/>
       </c>
       <c r="H40" s="9" t="inlineStr">
@@ -1441,70 +1450,70 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="37" t="inlineStr">
+      <c r="A41" s="36" t="inlineStr">
         <is>
           <t>★ 최종 신청 권장 (S등급 기준)</t>
         </is>
       </c>
-      <c r="B41" s="24" t="n"/>
-      <c r="C41" s="38">
+      <c r="B41" s="23" t="n"/>
+      <c r="C41" s="37">
         <f>C40</f>
         <v/>
       </c>
-      <c r="D41" s="38">
+      <c r="D41" s="37">
         <f>D40</f>
         <v/>
       </c>
-      <c r="E41" s="39">
+      <c r="E41" s="38">
         <f>E40</f>
         <v/>
       </c>
-      <c r="F41" s="38">
+      <c r="F41" s="37">
         <f>F40</f>
         <v/>
       </c>
-      <c r="G41" s="38">
+      <c r="G41" s="37">
         <f>G40</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="27" t="inlineStr">
+      <c r="A43" s="26" t="inlineStr">
         <is>
           <t>⑥ 비용 절감 수칙 (참고)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="40" t="inlineStr">
+      <c r="A44" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">  ① GPT Image 2 quality: medium 고정 — high 대비 약 75% 절감</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="40" t="inlineStr">
+      <c r="A45" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">  ② 개발 테스트는 Kling (저가) 우선, 중간점검·최종만 Seedance 2.0 사용</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="40" t="inlineStr">
+      <c r="A46" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">  ③ Claude 프롬프트는 간결하게 유지 — 불필요한 토큰 절감</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="40" t="inlineStr">
+      <c r="A47" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">  ④ fal.ai Hard Limit $50 설정 필수 — 대시보드 &gt; Billing &gt; Spend Limit</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="40" t="inlineStr">
+      <c r="A48" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">  ⑤ 주 1회 각 API 대시보드 사용량 확인 (OpenAI / fal.ai / Anthropic Console / AWS)</t>
         </is>

--- a/content/02_리서치/2026-06-30_API비용산정_근거.xlsx
+++ b/content/02_리서치/2026-06-30_API비용산정_근거.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,11 +62,6 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00C00000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00666666"/>
       <sz val="10"/>
     </font>
     <font>
@@ -132,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -152,19 +147,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -187,11 +182,6 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -204,16 +194,16 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -581,8 +571,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -597,7 +587,7 @@
     <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KX_A2 · 1개월 예상 비용 (청구용)</t>
+          <t>KX_A2 · 1개월 예상 비용 (청구용) — Claude Code Option A: Pro×6</t>
         </is>
       </c>
     </row>
@@ -608,7 +598,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1">
+    <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>환율 (KRW/USD)</t>
@@ -623,7 +613,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1">
+    <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>청구 기간</t>
@@ -642,7 +632,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1">
+    <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>항목</t>
@@ -676,7 +666,7 @@
       <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="6" t="inlineStr"/>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
+    <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Figma Professional (월간)</t>
@@ -692,7 +682,7 @@
         <f>B9*C9</f>
         <v/>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="4">
         <f>D9*$B$4</f>
         <v/>
       </c>
@@ -702,7 +692,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
+    <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Vercel</t>
@@ -714,7 +704,7 @@
       <c r="C10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="4" t="n">
@@ -726,7 +716,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
+    <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Supabase Pro</t>
@@ -742,7 +732,7 @@
         <f>B11*C11</f>
         <v/>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="4">
         <f>D11*$B$4</f>
         <v/>
       </c>
@@ -752,7 +742,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
+    <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>AWS (EC2·S3·RDS 예비 예산)</t>
@@ -768,7 +758,7 @@
         <f>B12*C12</f>
         <v/>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="4">
         <f>D12*$B$4</f>
         <v/>
       </c>
@@ -778,10 +768,10 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1">
+    <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>[Option A] Claude Code Pro × 6명</t>
+          <t>Claude Code Pro × 6명</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
@@ -794,130 +784,126 @@
         <f>B13*C13</f>
         <v/>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="4">
         <f>D13*$B$4</f>
         <v/>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Pro $20/유저 — 기본 플랜</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>[Option B] Claude Code Max×4 + Pro×2</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Max×4+Pro×2</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>6명</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>440</v>
-      </c>
-      <c r="E14" s="8">
+          <t>Pro $20/유저</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>고정 소계</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="10">
+        <f>SUM(D9:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="11">
         <f>D14*$B$4</f>
         <v/>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Max $100(BE2·FE1·UX1) + Pro $20(PM2) — 업그레이드 불가 시 권장</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>고정 소계 (Option A 기준)</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="7">
-        <f>D9+D10+D11+D12+D13</f>
-        <v/>
-      </c>
-      <c r="E15" s="8">
-        <f>D15*$B$4</f>
-        <v/>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>※ Option B 기준: D열 합계 $515</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    </row>
+    <row r="16" ht="16.5" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>② 사용량 기반 API — 토큰 기반 (Claude Sonnet)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>호출수</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>입력토큰/회</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>출력토큰/회</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>입력단가($/1M)</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>출력단가($/1M)</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>합계(USD)</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>합계(KRW)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Claude Sonnet — 프롬프트 보조 (F001)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G18" s="7">
+        <f>B18*(C18*E18+D18*F18)/1000000</f>
+        <v/>
+      </c>
+      <c r="H18" s="4">
+        <f>G18*$B$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Claude Sonnet — 프롬프트 보조 (F001)</t>
+          <t>Claude Sonnet — 역프롬프트 (F004, S등급)</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>3</v>
@@ -929,251 +915,244 @@
         <f>B19*(C19*E19+D19*F19)/1000000</f>
         <v/>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="4">
         <f>G19*$B$4</f>
         <v/>
       </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>이미지 프롬프트 생성 보조</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16.5" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Claude Sonnet — 역프롬프트 (F004, S등급)</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>800</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G20" s="7">
-        <f>B20*(C20*E20+D20*F20)/1000000</f>
-        <v/>
-      </c>
-      <c r="H20" s="8">
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>API 소계</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="10">
+        <f>SUM(G18:G19)</f>
+        <v/>
+      </c>
+      <c r="H20" s="11">
         <f>G20*$B$4</f>
         <v/>
       </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>역프롬프트 분석 (S등급 도전)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="16.5" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>API 소계</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="7">
-        <f>SUM(G19:G20)</f>
-        <v/>
-      </c>
-      <c r="H21" s="8">
-        <f>G21*$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="16.5" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    </row>
+    <row r="22" ht="16.5" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>③ 사용량 기반 — 이미지 생성 (GPT Image 2, quality: medium)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>이미지 수</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>단가/장(USD)</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>합계(USD)</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>합계(KRW)</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr"/>
-      <c r="H24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="16.5" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>GPT Image 2 medium — 단일 이미지 (F001)</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B24" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C24" s="5" t="n">
         <v>0.042</v>
       </c>
-      <c r="D25" s="7">
-        <f>B25*C25</f>
-        <v/>
-      </c>
-      <c r="E25" s="8">
-        <f>D25*$B$4</f>
-        <v/>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="D24" s="7">
+        <f>B24*C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="4">
+        <f>D24*$B$4</f>
+        <v/>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>이미지 생성 테스트+데모</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1">
-      <c r="A26" s="14" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>[B팀 제공] 9그리드 스토리보드</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n">
+      <c r="B25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="15" t="n">
+      <c r="C25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="D25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="17" t="n">
+      <c r="E25" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>B팀에서 생성 제공 → A2팀 비용 없음</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>이미지 소계</t>
         </is>
       </c>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="7">
-        <f>D25</f>
-        <v/>
-      </c>
-      <c r="E27" s="8">
-        <f>D27*$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="16.5" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="10">
+        <f>D24</f>
+        <v/>
+      </c>
+      <c r="E26" s="11">
+        <f>D26*$B$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="16.5" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>④ 사용량 기반 — 영상 생성 (fal.ai / 1세트 = 1클립)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  ℹ  흐름: [B팀] 9그리드 스토리보드 + shot1~9 프롬프트 제공  →  [A2팀] 영상 생성 API  →  클립 1개 출력</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>단가($/초)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>세트 수</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>초/클립</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>총 초</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>합계(USD)</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>합계(KRW)</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="16.5" customHeight="1">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>fal.ai Kling — 개발 테스트 (5초/클립)</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" s="5">
+        <f>C31*D31</f>
+        <v/>
+      </c>
+      <c r="F31" s="7">
+        <f>B31*E31</f>
+        <v/>
+      </c>
+      <c r="G31" s="4">
+        <f>F31*$B$4</f>
+        <v/>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>주 2회×4주 / 3~5초 상한 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>fal.ai Kling — 개발 테스트 (5초/클립)</t>
+          <t>fal.ai Seedance 2.0 — 중간점검 (5초/클립)</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>0.11</v>
+        <v>0.3034</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="5">
         <f>C32*D32</f>
         <v/>
       </c>
@@ -1181,32 +1160,32 @@
         <f>B32*E32</f>
         <v/>
       </c>
-      <c r="G32" s="8">
+      <c r="G32" s="4">
         <f>F32*$B$4</f>
         <v/>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>주 2회×4주 / 3~5초 상한 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16.5" customHeight="1">
+          <t>2주차 중간점검 데모 / 720p standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>fal.ai Seedance 2.0 — 중간점검 (5초/클립)</t>
+          <t>fal.ai Seedance 2.0 — 최종 출력 (15초/클립, 최대 길이)</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
         <v>0.3034</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E33" s="12">
+        <v>15</v>
+      </c>
+      <c r="E33" s="5">
         <f>C33*D33</f>
         <v/>
       </c>
@@ -1214,235 +1193,167 @@
         <f>B33*E33</f>
         <v/>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="4">
         <f>F33*$B$4</f>
         <v/>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>2주차 중간점검 데모 / 720p standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16.5" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>fal.ai Seedance 2.0 — 최종 출력 (15초/클립, 최대 길이)</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>0.3034</v>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E34" s="12">
-        <f>C34*D34</f>
-        <v/>
-      </c>
-      <c r="F34" s="7">
-        <f>B34*E34</f>
-        <v/>
-      </c>
-      <c r="G34" s="8">
+          <t>4주차 최종 발표 2세트 / 720p / 음성 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>영상 소계</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="10">
+        <f>SUM(F31:F33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="11">
         <f>F34*$B$4</f>
         <v/>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>4주차 최종 발표 2세트 / 720p / 음성 포함</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16.5" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>영상 소계</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="7">
-        <f>SUM(F32:F34)</f>
-        <v/>
-      </c>
-      <c r="G35" s="8">
-        <f>F35*$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="16.5" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  ★ fal.ai Hard Limit 권장 $50 설정 (Billing &gt; Spend Limit)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37" ht="16.5" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>■ 요약</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr"/>
-      <c r="E39" s="6" t="inlineStr"/>
-      <c r="F39" s="6" t="inlineStr"/>
-      <c r="G39" s="6" t="inlineStr"/>
-      <c r="H39" s="6" t="inlineStr"/>
-    </row>
-    <row r="40" ht="16.5" customHeight="1">
+      <c r="D38" s="6" t="inlineStr"/>
+      <c r="E38" s="6" t="inlineStr"/>
+      <c r="F38" s="6" t="inlineStr"/>
+      <c r="G38" s="6" t="inlineStr"/>
+      <c r="H38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>① 고정 구독 소계</t>
+        </is>
+      </c>
+      <c r="B39" s="18">
+        <f>D14</f>
+        <v/>
+      </c>
+      <c r="C39" s="19">
+        <f>E14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>① 고정 구독 소계 (Option A)</t>
-        </is>
-      </c>
-      <c r="B40" s="20">
-        <f>D15</f>
-        <v/>
-      </c>
-      <c r="C40" s="21">
-        <f>E15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="16.5" customHeight="1">
-      <c r="A41" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  └ Option B 기준 시</t>
-        </is>
-      </c>
-      <c r="B41" s="23">
-        <f>D9+D10+D11+D12+D14</f>
-        <v/>
-      </c>
-      <c r="C41" s="24">
+          <t>②③④ API/이미지/영상 소계 (B등급)</t>
+        </is>
+      </c>
+      <c r="B40" s="18">
+        <f>D26+F31+F32+G18</f>
+        <v/>
+      </c>
+      <c r="C40" s="19">
+        <f>B40*$B$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>②③④ API/이미지/영상 소계 (S등급 도전)</t>
+        </is>
+      </c>
+      <c r="B41" s="18">
+        <f>D26+F31+F32+F33+G18+G19</f>
+        <v/>
+      </c>
+      <c r="C41" s="19">
         <f>B41*$B$4</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>②③④ API/이미지/영상 소계 (B등급)</t>
-        </is>
-      </c>
-      <c r="B42" s="20">
-        <f>D27+F32+F33+G19</f>
-        <v/>
-      </c>
-      <c r="C42" s="21">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>★ 총 합계 — B등급</t>
+        </is>
+      </c>
+      <c r="B42" s="21">
+        <f>D14+B40</f>
+        <v/>
+      </c>
+      <c r="C42" s="22">
         <f>B42*$B$4</f>
         <v/>
       </c>
-    </row>
-    <row r="43" ht="16.5" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>②③④ API/이미지/영상 소계 (S등급 도전)</t>
-        </is>
-      </c>
-      <c r="B43" s="20">
-        <f>D27+F32+F33+F34+G19+G20</f>
-        <v/>
-      </c>
-      <c r="C43" s="21">
+      <c r="D42" s="23" t="n"/>
+      <c r="E42" s="23" t="n"/>
+      <c r="F42" s="23" t="n"/>
+      <c r="G42" s="23" t="n"/>
+      <c r="H42" s="23" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>★ 총 합계 — S등급 (권장)</t>
+        </is>
+      </c>
+      <c r="B43" s="25">
+        <f>D14+B41</f>
+        <v/>
+      </c>
+      <c r="C43" s="26">
         <f>B43*$B$4</f>
         <v/>
       </c>
-    </row>
-    <row r="44" ht="16.5" customHeight="1">
-      <c r="A44" s="25" t="inlineStr">
-        <is>
-          <t>★ 총 합계 — B등급 · Option A</t>
-        </is>
-      </c>
-      <c r="B44" s="26">
-        <f>D15+D27+F32+F33+G19</f>
-        <v/>
-      </c>
-      <c r="C44" s="27">
-        <f>B44*$B$4</f>
-        <v/>
-      </c>
-      <c r="D44" s="28" t="n"/>
-      <c r="E44" s="28" t="n"/>
-      <c r="F44" s="28" t="n"/>
-      <c r="G44" s="28" t="n"/>
-      <c r="H44" s="28" t="n"/>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="29" t="inlineStr">
-        <is>
-          <t>★ 총 합계 — S등급 · Option A (권장)</t>
-        </is>
-      </c>
-      <c r="B45" s="30">
-        <f>D15+B43</f>
-        <v/>
-      </c>
-      <c r="C45" s="31">
-        <f>B45*$B$4</f>
-        <v/>
-      </c>
-      <c r="D45" s="32" t="n"/>
-      <c r="E45" s="32" t="n"/>
-      <c r="F45" s="32" t="n"/>
-      <c r="G45" s="32" t="n"/>
-      <c r="H45" s="32" t="n"/>
-    </row>
-    <row r="46" ht="16.5" customHeight="1">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>★ 총 합계 — S등급 · Option B</t>
-        </is>
-      </c>
-      <c r="B46" s="26">
-        <f>D9+D10+D11+D12+D14+B43</f>
-        <v/>
-      </c>
-      <c r="C46" s="27">
-        <f>B46*$B$4</f>
-        <v/>
-      </c>
-      <c r="D46" s="28" t="n"/>
-      <c r="E46" s="28" t="n"/>
-      <c r="F46" s="28" t="n"/>
-      <c r="G46" s="28" t="n"/>
-      <c r="H46" s="28" t="n"/>
+      <c r="D43" s="27" t="n"/>
+      <c r="E43" s="27" t="n"/>
+      <c r="F43" s="27" t="n"/>
+      <c r="G43" s="27" t="n"/>
+      <c r="H43" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A22:H22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/02_리서치/2026-06-30_API비용산정_근거.xlsx
+++ b/content/02_리서치/2026-06-30_API비용산정_근거.xlsx
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -591,7 +591,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1">
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>■ 가정 (Assumptions)</t>
@@ -625,7 +625,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1">
+    <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>① 고정 구독 (월 정액)</t>
@@ -811,7 +811,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1">
+    <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>② 사용량 기반 API — 토큰 기반 (Claude Sonnet)</t>
@@ -940,7 +940,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1">
+    <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>③ 사용량 기반 — 이미지 생성 (GPT Image 2, quality: medium)</t>
@@ -1048,7 +1048,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1">
+    <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>④ 사용량 기반 — 영상 생성 (fal.ai / 1세트 = 1클립)</t>
@@ -1133,21 +1133,21 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>주 2회×4주 / 3~5초 상한 기준</t>
+          <t>1주차~4주차 / BE 주 2회 × 4주 / 3~5초 상한 기준</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>fal.ai Seedance 2.0 — 중간점검 (5초/클립)</t>
+          <t>fal.ai Seedance 2.0 — 2주차 중간점검 (5초/클립)</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
         <v>0.3034</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D32" s="5" t="n">
         <v>5</v>
@@ -1166,24 +1166,24 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>2주차 중간점검 데모 / 720p standard</t>
+          <t>BE 연동 3+품질 3+PM확인 2+리허설 1+데모 1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>fal.ai Seedance 2.0 — 최종 출력 (15초/클립, 최대 길이)</t>
+          <t>fal.ai Seedance 2.0 — 3주차 품질 확인 (10초/클립)</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
         <v>0.3034</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E33" s="5">
         <f>C33*D33</f>
@@ -1199,103 +1199,121 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>4주차 최종 발표 2세트 / 720p / 음성 포함</t>
+          <t>BE 품질조정 3+PM검수 2+팀리뷰 1</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>fal.ai Seedance 2.0 — 4주차 최종 출력 (15초/클립, 최대 길이)</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E34" s="5">
+        <f>C34*D34</f>
+        <v/>
+      </c>
+      <c r="F34" s="7">
+        <f>B34*E34</f>
+        <v/>
+      </c>
+      <c r="G34" s="4">
+        <f>F34*$B$4</f>
+        <v/>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>BE확인 2+PM검수 2+리허설 1+최종발표 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>영상 소계</t>
         </is>
       </c>
-      <c r="B34" s="9" t="n"/>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="10">
-        <f>SUM(F31:F33)</f>
-        <v/>
-      </c>
-      <c r="G34" s="11">
-        <f>F34*$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ★ fal.ai Hard Limit 권장 $50 설정 (Billing &gt; Spend Limit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="16.5" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="10">
+        <f>SUM(F31:F34)</f>
+        <v/>
+      </c>
+      <c r="G35" s="11">
+        <f>F35*$B$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ★ fal.ai Hard Limit 권장 $100 설정 (Billing &gt; Spend Limit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>■ 요약</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr"/>
-      <c r="E38" s="6" t="inlineStr"/>
-      <c r="F38" s="6" t="inlineStr"/>
-      <c r="G38" s="6" t="inlineStr"/>
-      <c r="H38" s="6" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>① 고정 구독 소계</t>
-        </is>
-      </c>
-      <c r="B39" s="18">
-        <f>D14</f>
-        <v/>
-      </c>
-      <c r="C39" s="19">
-        <f>E14</f>
-        <v/>
-      </c>
+      <c r="D39" s="6" t="inlineStr"/>
+      <c r="E39" s="6" t="inlineStr"/>
+      <c r="F39" s="6" t="inlineStr"/>
+      <c r="G39" s="6" t="inlineStr"/>
+      <c r="H39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>②③④ API/이미지/영상 소계 (B등급)</t>
+          <t>① 고정 구독 소계</t>
         </is>
       </c>
       <c r="B40" s="18">
-        <f>D26+F31+F32+G18</f>
+        <f>D14</f>
         <v/>
       </c>
       <c r="C40" s="19">
-        <f>B40*$B$4</f>
+        <f>E14</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>②③④ API/이미지/영상 소계 (S등급 도전)</t>
+          <t>②③④ API/이미지/영상 소계 (B등급)</t>
         </is>
       </c>
       <c r="B41" s="18">
-        <f>D26+F31+F32+F33+G18+G19</f>
+        <f>D26+F31+F32+F33+G18</f>
         <v/>
       </c>
       <c r="C41" s="19">
@@ -1303,56 +1321,71 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="16.5" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>②③④ API/이미지/영상 소계 (S등급 도전)</t>
+        </is>
+      </c>
+      <c r="B42" s="18">
+        <f>D26+F31+F32+F33+F34+G18+G19</f>
+        <v/>
+      </c>
+      <c r="C42" s="19">
+        <f>B42*$B$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="16.5" customHeight="1">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>★ 총 합계 — B등급</t>
         </is>
       </c>
-      <c r="B42" s="21">
-        <f>D14+B40</f>
-        <v/>
-      </c>
-      <c r="C42" s="22">
-        <f>B42*$B$4</f>
-        <v/>
-      </c>
-      <c r="D42" s="23" t="n"/>
-      <c r="E42" s="23" t="n"/>
-      <c r="F42" s="23" t="n"/>
-      <c r="G42" s="23" t="n"/>
-      <c r="H42" s="23" t="n"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="24" t="inlineStr">
+      <c r="B43" s="21">
+        <f>D14+B41</f>
+        <v/>
+      </c>
+      <c r="C43" s="22">
+        <f>B43*$B$4</f>
+        <v/>
+      </c>
+      <c r="D43" s="23" t="n"/>
+      <c r="E43" s="23" t="n"/>
+      <c r="F43" s="23" t="n"/>
+      <c r="G43" s="23" t="n"/>
+      <c r="H43" s="23" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="24" t="inlineStr">
         <is>
           <t>★ 총 합계 — S등급 (권장)</t>
         </is>
       </c>
-      <c r="B43" s="25">
-        <f>D14+B41</f>
-        <v/>
-      </c>
-      <c r="C43" s="26">
-        <f>B43*$B$4</f>
-        <v/>
-      </c>
-      <c r="D43" s="27" t="n"/>
-      <c r="E43" s="27" t="n"/>
-      <c r="F43" s="27" t="n"/>
-      <c r="G43" s="27" t="n"/>
-      <c r="H43" s="27" t="n"/>
+      <c r="B44" s="25">
+        <f>D14+B42</f>
+        <v/>
+      </c>
+      <c r="C44" s="26">
+        <f>B44*$B$4</f>
+        <v/>
+      </c>
+      <c r="D44" s="27" t="n"/>
+      <c r="E44" s="27" t="n"/>
+      <c r="F44" s="27" t="n"/>
+      <c r="G44" s="27" t="n"/>
+      <c r="H44" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A29:H29"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A22:H22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
